--- a/output_data/charts/crashSeverityByType-Union.xlsx
+++ b/output_data/charts/crashSeverityByType-Union.xlsx
@@ -31,40 +31,40 @@
     <t>Fixed Object</t>
   </si>
   <si>
+    <t>Angle</t>
+  </si>
+  <si>
     <t>Left Turn</t>
   </si>
   <si>
-    <t>Angle</t>
-  </si>
-  <si>
     <t>Overturning</t>
   </si>
   <si>
+    <t>Head On</t>
+  </si>
+  <si>
     <t>Pedestrian</t>
   </si>
   <si>
+    <t>Animal</t>
+  </si>
+  <si>
+    <t>Parked Vehicle</t>
+  </si>
+  <si>
     <t>Rear End</t>
   </si>
   <si>
-    <t>Head On</t>
-  </si>
-  <si>
-    <t>Animal</t>
-  </si>
-  <si>
     <t>Backing</t>
   </si>
   <si>
+    <t>Other Non-Collision</t>
+  </si>
+  <si>
     <t>Other Object</t>
   </si>
   <si>
-    <t>Other Non-Collision</t>
-  </si>
-  <si>
     <t>Pedalcycles</t>
-  </si>
-  <si>
-    <t>Parked Vehicle</t>
   </si>
   <si>
     <t>Right Turn</t>
@@ -216,40 +216,40 @@
                   <c:v>Fixed Object</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>Angle</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Left Turn</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Angle</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>Overturning</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>Head On</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Pedestrian</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
+                  <c:v>Animal</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Parked Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>Rear End</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>Head On</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Animal</c:v>
-                </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>Backing</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Other Object</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>Other Non-Collision</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>Other Object</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>Pedalcycles</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Parked Vehicle</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>Right Turn</c:v>
@@ -273,31 +273,31 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>29.03225806451613</c:v>
+                  <c:v>39.39393939393939</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>19.35483870967742</c:v>
+                  <c:v>15.15151515151515</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>16.12903225806452</c:v>
+                  <c:v>15.15151515151515</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>9.67741935483871</c:v>
+                  <c:v>9.090909090909092</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>9.67741935483871</c:v>
+                  <c:v>6.060606060606061</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.451612903225806</c:v>
+                  <c:v>6.060606060606061</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>6.451612903225806</c:v>
+                  <c:v>3.03030303030303</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.225806451612903</c:v>
+                  <c:v>3.03030303030303</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>0</c:v>
+                  <c:v>3.03030303030303</c:v>
                 </c:pt>
                 <c:pt idx="9">
                   <c:v>0</c:v>
@@ -358,40 +358,40 @@
                   <c:v>Fixed Object</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>Angle</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Left Turn</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Angle</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>Overturning</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>Head On</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Pedestrian</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
+                  <c:v>Animal</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Parked Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>Rear End</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>Head On</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Animal</c:v>
-                </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>Backing</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Other Object</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>Other Non-Collision</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>Other Object</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>Pedalcycles</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Parked Vehicle</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>Right Turn</c:v>
@@ -415,49 +415,49 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>26.78571428571428</c:v>
+                  <c:v>26.13636363636364</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>6.547619047619048</c:v>
+                  <c:v>22.72727272727273</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>25.59523809523809</c:v>
+                  <c:v>7.954545454545454</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4.761904761904762</c:v>
+                  <c:v>3.409090909090909</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1.19047619047619</c:v>
+                  <c:v>9.659090909090908</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6.547619047619048</c:v>
+                  <c:v>2.272727272727273</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>9.523809523809524</c:v>
+                  <c:v>3.409090909090909</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>3.571428571428571</c:v>
+                  <c:v>1.704545454545454</c:v>
                 </c:pt>
                 <c:pt idx="8">
+                  <c:v>7.954545454545454</c:v>
+                </c:pt>
+                <c:pt idx="9">
                   <c:v>0</c:v>
                 </c:pt>
-                <c:pt idx="9">
-                  <c:v>0.5952380952380952</c:v>
-                </c:pt>
                 <c:pt idx="10">
-                  <c:v>3.571428571428571</c:v>
+                  <c:v>4.545454545454546</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1.19047619047619</c:v>
+                  <c:v>0.5681818181818182</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>1.19047619047619</c:v>
+                  <c:v>1.136363636363636</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>1.19047619047619</c:v>
+                  <c:v>1.136363636363636</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>7.738095238095238</c:v>
+                  <c:v>7.386363636363637</c:v>
                 </c:pt>
                 <c:pt idx="15">
                   <c:v>0</c:v>
@@ -500,40 +500,40 @@
                   <c:v>Fixed Object</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>Angle</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>Left Turn</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Angle</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>Overturning</c:v>
                 </c:pt>
                 <c:pt idx="4">
+                  <c:v>Head On</c:v>
+                </c:pt>
+                <c:pt idx="5">
                   <c:v>Pedestrian</c:v>
                 </c:pt>
-                <c:pt idx="5">
+                <c:pt idx="6">
+                  <c:v>Animal</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Parked Vehicle</c:v>
+                </c:pt>
+                <c:pt idx="8">
                   <c:v>Rear End</c:v>
                 </c:pt>
-                <c:pt idx="6">
-                  <c:v>Head On</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Animal</c:v>
-                </c:pt>
-                <c:pt idx="8">
+                <c:pt idx="9">
                   <c:v>Backing</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Other Object</c:v>
                 </c:pt>
                 <c:pt idx="10">
                   <c:v>Other Non-Collision</c:v>
                 </c:pt>
                 <c:pt idx="11">
+                  <c:v>Other Object</c:v>
+                </c:pt>
+                <c:pt idx="12">
                   <c:v>Pedalcycles</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Parked Vehicle</c:v>
                 </c:pt>
                 <c:pt idx="13">
                   <c:v>Right Turn</c:v>
@@ -557,55 +557,55 @@
                 <c:formatCode>General</c:formatCode>
                 <c:ptCount val="17"/>
                 <c:pt idx="0">
-                  <c:v>20.32456278556798</c:v>
+                  <c:v>19.75910962036896</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3.686781156451867</c:v>
+                  <c:v>10.9772831224272</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>10.41436899322515</c:v>
+                  <c:v>4.192712303704833</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1.386481802426343</c:v>
+                  <c:v>1.28068303094984</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>0.3308649755790137</c:v>
+                  <c:v>1.73806982771764</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>20.07247518512683</c:v>
+                  <c:v>0.3811556639731666</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>1.59130297778478</c:v>
+                  <c:v>18.82908980027443</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>19.31621238380337</c:v>
+                  <c:v>2.92727549931392</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>3.072317630376556</c:v>
+                  <c:v>19.80484830004574</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>0.5514416259650229</c:v>
+                  <c:v>3.079737764903186</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2.158500078777375</c:v>
+                  <c:v>2.027748132337246</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>0.2520876004411533</c:v>
+                  <c:v>0.5641103826802867</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>2.741452654797542</c:v>
+                  <c:v>0.2591858515017533</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>2.063967228611943</c:v>
+                  <c:v>2.0582405854551</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>11.12336536946589</c:v>
+                  <c:v>11.14499161457539</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>0.03151095005514416</c:v>
+                  <c:v>0.03049245311785333</c:v>
                 </c:pt>
                 <c:pt idx="16">
-                  <c:v>0.8823066015440365</c:v>
+                  <c:v>0.9452660466534533</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1061,13 +1061,13 @@
         <v>4</v>
       </c>
       <c r="B2" s="2">
-        <v>29.03225806451613</v>
+        <v>39.39393939393939</v>
       </c>
       <c r="C2" s="2">
-        <v>26.78571428571428</v>
+        <v>26.13636363636364</v>
       </c>
       <c r="D2" s="2">
-        <v>20.32456278556798</v>
+        <v>19.75910962036896</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1075,13 +1075,13 @@
         <v>5</v>
       </c>
       <c r="B3" s="2">
-        <v>19.35483870967742</v>
+        <v>15.15151515151515</v>
       </c>
       <c r="C3" s="2">
-        <v>6.547619047619048</v>
+        <v>22.72727272727273</v>
       </c>
       <c r="D3" s="2">
-        <v>3.686781156451867</v>
+        <v>10.9772831224272</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1089,13 +1089,13 @@
         <v>6</v>
       </c>
       <c r="B4" s="2">
-        <v>16.12903225806452</v>
+        <v>15.15151515151515</v>
       </c>
       <c r="C4" s="2">
-        <v>25.59523809523809</v>
+        <v>7.954545454545454</v>
       </c>
       <c r="D4" s="2">
-        <v>10.41436899322515</v>
+        <v>4.192712303704833</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1103,13 +1103,13 @@
         <v>7</v>
       </c>
       <c r="B5" s="2">
-        <v>9.67741935483871</v>
+        <v>9.090909090909092</v>
       </c>
       <c r="C5" s="2">
-        <v>4.761904761904762</v>
+        <v>3.409090909090909</v>
       </c>
       <c r="D5" s="2">
-        <v>1.386481802426343</v>
+        <v>1.28068303094984</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1117,13 +1117,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="2">
-        <v>9.67741935483871</v>
+        <v>6.060606060606061</v>
       </c>
       <c r="C6" s="2">
-        <v>1.19047619047619</v>
+        <v>9.659090909090908</v>
       </c>
       <c r="D6" s="2">
-        <v>0.3308649755790137</v>
+        <v>1.73806982771764</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1131,13 +1131,13 @@
         <v>9</v>
       </c>
       <c r="B7" s="2">
-        <v>6.451612903225806</v>
+        <v>6.060606060606061</v>
       </c>
       <c r="C7" s="2">
-        <v>6.547619047619048</v>
+        <v>2.272727272727273</v>
       </c>
       <c r="D7" s="2">
-        <v>20.07247518512683</v>
+        <v>0.3811556639731666</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1145,13 +1145,13 @@
         <v>10</v>
       </c>
       <c r="B8" s="2">
-        <v>6.451612903225806</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="C8" s="2">
-        <v>9.523809523809524</v>
+        <v>3.409090909090909</v>
       </c>
       <c r="D8" s="2">
-        <v>1.59130297778478</v>
+        <v>18.82908980027443</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1159,13 +1159,13 @@
         <v>11</v>
       </c>
       <c r="B9" s="2">
-        <v>3.225806451612903</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="C9" s="2">
-        <v>3.571428571428571</v>
+        <v>1.704545454545454</v>
       </c>
       <c r="D9" s="2">
-        <v>19.31621238380337</v>
+        <v>2.92727549931392</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1173,13 +1173,13 @@
         <v>12</v>
       </c>
       <c r="B10" s="2">
-        <v>0</v>
+        <v>3.03030303030303</v>
       </c>
       <c r="C10" s="2">
-        <v>0</v>
+        <v>7.954545454545454</v>
       </c>
       <c r="D10" s="2">
-        <v>3.072317630376556</v>
+        <v>19.80484830004574</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1190,10 +1190,10 @@
         <v>0</v>
       </c>
       <c r="C11" s="2">
-        <v>0.5952380952380952</v>
+        <v>0</v>
       </c>
       <c r="D11" s="2">
-        <v>0.5514416259650229</v>
+        <v>3.079737764903186</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1204,10 +1204,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="2">
-        <v>3.571428571428571</v>
+        <v>4.545454545454546</v>
       </c>
       <c r="D12" s="2">
-        <v>2.158500078777375</v>
+        <v>2.027748132337246</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1218,10 +1218,10 @@
         <v>0</v>
       </c>
       <c r="C13" s="2">
-        <v>1.19047619047619</v>
+        <v>0.5681818181818182</v>
       </c>
       <c r="D13" s="2">
-        <v>0.2520876004411533</v>
+        <v>0.5641103826802867</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1232,10 +1232,10 @@
         <v>0</v>
       </c>
       <c r="C14" s="2">
-        <v>1.19047619047619</v>
+        <v>1.136363636363636</v>
       </c>
       <c r="D14" s="2">
-        <v>2.741452654797542</v>
+        <v>0.2591858515017533</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1246,10 +1246,10 @@
         <v>0</v>
       </c>
       <c r="C15" s="2">
-        <v>1.19047619047619</v>
+        <v>1.136363636363636</v>
       </c>
       <c r="D15" s="2">
-        <v>2.063967228611943</v>
+        <v>2.0582405854551</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1260,10 +1260,10 @@
         <v>0</v>
       </c>
       <c r="C16" s="2">
-        <v>7.738095238095238</v>
+        <v>7.386363636363637</v>
       </c>
       <c r="D16" s="2">
-        <v>11.12336536946589</v>
+        <v>11.14499161457539</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -1277,7 +1277,7 @@
         <v>0</v>
       </c>
       <c r="D17" s="2">
-        <v>0.03151095005514416</v>
+        <v>0.03049245311785333</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -1291,7 +1291,7 @@
         <v>0</v>
       </c>
       <c r="D18" s="2">
-        <v>0.8823066015440365</v>
+        <v>0.9452660466534533</v>
       </c>
     </row>
   </sheetData>

--- a/output_data/charts/crashSeverityByType-Union.xlsx
+++ b/output_data/charts/crashSeverityByType-Union.xlsx
@@ -83,8 +83,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode=""/>
+    <numFmt numFmtId="165" formatCode="0.00"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -141,7 +142,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -173,7 +174,7 @@
               <a:rPr lang="en-US" sz="1400" baseline="0">
                 <a:latin typeface="Arial"/>
               </a:rPr>
-              <a:t>Crash Severity by Type of Crash - Union County</a:t>
+              <a:t>Crash Severity by Type of Crash, Union County, 2020-2024</a:t>
             </a:r>
           </a:p>
         </c:rich>
